--- a/bills/JXZFSP01/-1003733706693/6d85008f7f7972fd90832a1022876df384976a1165aef80c1e3f256d2e720bdf/bill-all.xlsx
+++ b/bills/JXZFSP01/-1003733706693/6d85008f7f7972fd90832a1022876df384976a1165aef80c1e3f256d2e720bdf/bill-all.xlsx
@@ -241,59 +241,86 @@
         </is>
       </c>
     </row>
-    <row r="13"/>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>总计</t>
-        </is>
-      </c>
-    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>08/24 09:45:46</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>46380</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>jxxiaomei521</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="14"/>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>总入款</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>756000</t>
+          <t>总计</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>应下发</t>
+          <t>总入款</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>92760.74</t>
+          <t>756000</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>已下发</t>
+          <t>应下发</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>92760.74</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
+          <t>已下发</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>46380</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
           <t>未下发</t>
         </is>
       </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>92760.74</t>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>46380.74</t>
         </is>
       </c>
     </row>

--- a/bills/JXZFSP01/-1003733706693/6d85008f7f7972fd90832a1022876df384976a1165aef80c1e3f256d2e720bdf/bill-all.xlsx
+++ b/bills/JXZFSP01/-1003733706693/6d85008f7f7972fd90832a1022876df384976a1165aef80c1e3f256d2e720bdf/bill-all.xlsx
@@ -75,12 +75,12 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>08/24 08:22:11</t>
+          <t>08/25 11:41:35</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>378000</t>
+          <t>100000</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -95,7 +95,7 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>46380.37</t>
+          <t>12269.94</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -105,7 +105,7 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>xinhui9</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -117,210 +117,252 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
+          <t>08/24 08:22:11</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>378000</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>8.15</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>46380.37</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>tiantiananxin</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
           <t>08/24 08:03:39</t>
         </is>
       </c>
-      <c r="B6" t="inlineStr">
+      <c r="B7" t="inlineStr">
         <is>
           <t>378000</t>
         </is>
       </c>
-      <c r="C6" t="inlineStr">
+      <c r="C7" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
       </c>
-      <c r="D6" t="inlineStr">
+      <c r="D7" t="inlineStr">
         <is>
           <t>8.15</t>
         </is>
       </c>
-      <c r="E6" t="inlineStr">
+      <c r="E7" t="inlineStr">
         <is>
           <t>46380.37</t>
         </is>
       </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="G6" t="inlineStr">
+      <c r="F7" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
         <is>
           <t>xinhui9</t>
         </is>
       </c>
-      <c r="H6" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-    </row>
-    <row r="7"/>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>代付</t>
-        </is>
-      </c>
-    </row>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="8"/>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
+          <t>代付</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
           <t>时间</t>
         </is>
       </c>
-      <c r="B9" t="inlineStr">
+      <c r="B10" t="inlineStr">
         <is>
           <t>金额</t>
         </is>
       </c>
-      <c r="C9" t="inlineStr">
+      <c r="C10" t="inlineStr">
         <is>
           <t>费率</t>
         </is>
       </c>
-      <c r="D9" t="inlineStr">
+      <c r="D10" t="inlineStr">
         <is>
           <t>汇率</t>
         </is>
       </c>
-      <c r="E9" t="inlineStr">
+      <c r="E10" t="inlineStr">
         <is>
           <t>结算</t>
         </is>
       </c>
-      <c r="F9" t="inlineStr">
+      <c r="F10" t="inlineStr">
         <is>
           <t>标记人</t>
         </is>
       </c>
-      <c r="G9" t="inlineStr">
+      <c r="G10" t="inlineStr">
         <is>
           <t>操作人</t>
         </is>
       </c>
-      <c r="H9" t="inlineStr">
+      <c r="H10" t="inlineStr">
         <is>
           <t>备注</t>
         </is>
       </c>
     </row>
-    <row r="10"/>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>下发</t>
-        </is>
-      </c>
-    </row>
+    <row r="11"/>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>时间</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>金额</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>标记人</t>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t>操作人</t>
-        </is>
-      </c>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t>备注</t>
+          <t>下发</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
+          <t>时间</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>金额</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>标记人</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>操作人</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>备注</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
           <t>08/24 09:45:46</t>
         </is>
       </c>
-      <c r="B13" t="inlineStr">
+      <c r="B14" t="inlineStr">
         <is>
           <t>46380</t>
         </is>
       </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="D13" t="inlineStr">
+      <c r="C14" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
         <is>
           <t>jxxiaomei521</t>
         </is>
       </c>
-      <c r="E13" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-    </row>
-    <row r="14"/>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>总计</t>
-        </is>
-      </c>
-    </row>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="15"/>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>总入款</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>756000</t>
+          <t>总计</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>应下发</t>
+          <t>总入款</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>92760.74</t>
+          <t>856000</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>已下发</t>
+          <t>应下发</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>46380</t>
+          <t>105030.67</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
+          <t>已下发</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>46380</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
           <t>未下发</t>
         </is>
       </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>46380.74</t>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>58650.67</t>
         </is>
       </c>
     </row>

--- a/bills/JXZFSP01/-1003733706693/6d85008f7f7972fd90832a1022876df384976a1165aef80c1e3f256d2e720bdf/bill-all.xlsx
+++ b/bills/JXZFSP01/-1003733706693/6d85008f7f7972fd90832a1022876df384976a1165aef80c1e3f256d2e720bdf/bill-all.xlsx
@@ -286,83 +286,110 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
+          <t>08/25 12:50:23</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>12269</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>jxxiaomei521</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
           <t>08/24 09:45:46</t>
         </is>
       </c>
-      <c r="B14" t="inlineStr">
+      <c r="B15" t="inlineStr">
         <is>
           <t>46380</t>
         </is>
       </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="D14" t="inlineStr">
+      <c r="C15" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
         <is>
           <t>jxxiaomei521</t>
         </is>
       </c>
-      <c r="E14" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-    </row>
-    <row r="15"/>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>总计</t>
-        </is>
-      </c>
-    </row>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="16"/>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>总入款</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>856000</t>
+          <t>总计</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>应下发</t>
+          <t>总入款</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>105030.67</t>
+          <t>856000</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>已下发</t>
+          <t>应下发</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>46380</t>
+          <t>105030.67</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
+          <t>已下发</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>58649</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
           <t>未下发</t>
         </is>
       </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>58650.67</t>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>46381.67</t>
         </is>
       </c>
     </row>

--- a/bills/JXZFSP01/-1003733706693/6d85008f7f7972fd90832a1022876df384976a1165aef80c1e3f256d2e720bdf/bill-all.xlsx
+++ b/bills/JXZFSP01/-1003733706693/6d85008f7f7972fd90832a1022876df384976a1165aef80c1e3f256d2e720bdf/bill-all.xlsx
@@ -75,7 +75,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>08/25 11:41:35</t>
+          <t>09/02 09:22:19</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -90,12 +90,12 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>8.15</t>
+          <t>8.2</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>12269.94</t>
+          <t>12195.12</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -117,12 +117,12 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>08/24 08:22:11</t>
+          <t>08/25 11:41:35</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>378000</t>
+          <t>100000</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -137,7 +137,7 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>46380.37</t>
+          <t>12269.94</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -147,7 +147,7 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>xinhui9</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -159,237 +159,279 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
+          <t>08/24 08:22:11</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>378000</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>8.15</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>46380.37</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>tiantiananxin</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
           <t>08/24 08:03:39</t>
         </is>
       </c>
-      <c r="B7" t="inlineStr">
+      <c r="B8" t="inlineStr">
         <is>
           <t>378000</t>
         </is>
       </c>
-      <c r="C7" t="inlineStr">
+      <c r="C8" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
       </c>
-      <c r="D7" t="inlineStr">
+      <c r="D8" t="inlineStr">
         <is>
           <t>8.15</t>
         </is>
       </c>
-      <c r="E7" t="inlineStr">
+      <c r="E8" t="inlineStr">
         <is>
           <t>46380.37</t>
         </is>
       </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="G7" t="inlineStr">
+      <c r="F8" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
         <is>
           <t>xinhui9</t>
         </is>
       </c>
-      <c r="H7" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-    </row>
-    <row r="8"/>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>代付</t>
-        </is>
-      </c>
-    </row>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="9"/>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
+          <t>代付</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
           <t>时间</t>
         </is>
       </c>
-      <c r="B10" t="inlineStr">
+      <c r="B11" t="inlineStr">
         <is>
           <t>金额</t>
         </is>
       </c>
-      <c r="C10" t="inlineStr">
+      <c r="C11" t="inlineStr">
         <is>
           <t>费率</t>
         </is>
       </c>
-      <c r="D10" t="inlineStr">
+      <c r="D11" t="inlineStr">
         <is>
           <t>汇率</t>
         </is>
       </c>
-      <c r="E10" t="inlineStr">
+      <c r="E11" t="inlineStr">
         <is>
           <t>结算</t>
         </is>
       </c>
-      <c r="F10" t="inlineStr">
+      <c r="F11" t="inlineStr">
         <is>
           <t>标记人</t>
         </is>
       </c>
-      <c r="G10" t="inlineStr">
+      <c r="G11" t="inlineStr">
         <is>
           <t>操作人</t>
         </is>
       </c>
-      <c r="H10" t="inlineStr">
+      <c r="H11" t="inlineStr">
         <is>
           <t>备注</t>
         </is>
       </c>
     </row>
-    <row r="11"/>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>下发</t>
-        </is>
-      </c>
-    </row>
+    <row r="12"/>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>时间</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>金额</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>标记人</t>
-        </is>
-      </c>
-      <c r="D13" t="inlineStr">
-        <is>
-          <t>操作人</t>
-        </is>
-      </c>
-      <c r="E13" t="inlineStr">
-        <is>
-          <t>备注</t>
+          <t>下发</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>08/25 12:50:23</t>
+          <t>时间</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>12269</t>
+          <t>金额</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t/>
+          <t>标记人</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>操作人</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t/>
+          <t>备注</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
+          <t>08/25 12:50:23</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>12269</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>jxxiaomei521</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
           <t>08/24 09:45:46</t>
         </is>
       </c>
-      <c r="B15" t="inlineStr">
+      <c r="B16" t="inlineStr">
         <is>
           <t>46380</t>
         </is>
       </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="D15" t="inlineStr">
+      <c r="C16" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
         <is>
           <t>jxxiaomei521</t>
         </is>
       </c>
-      <c r="E15" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-    </row>
-    <row r="16"/>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>总计</t>
-        </is>
-      </c>
-    </row>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="17"/>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>总入款</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>856000</t>
+          <t>总计</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>应下发</t>
+          <t>总入款</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>105030.67</t>
+          <t>956000</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>已下发</t>
+          <t>应下发</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>58649</t>
+          <t>117225.8</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
+          <t>已下发</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>58649</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
           <t>未下发</t>
         </is>
       </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>46381.67</t>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>58576.8</t>
         </is>
       </c>
     </row>

--- a/bills/JXZFSP01/-1003733706693/6d85008f7f7972fd90832a1022876df384976a1165aef80c1e3f256d2e720bdf/bill-all.xlsx
+++ b/bills/JXZFSP01/-1003733706693/6d85008f7f7972fd90832a1022876df384976a1165aef80c1e3f256d2e720bdf/bill-all.xlsx
@@ -328,12 +328,12 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>08/25 12:50:23</t>
+          <t>09/02 11:07:38</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>12269</t>
+          <t>12195</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -355,83 +355,110 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
+          <t>08/25 12:50:23</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>12269</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>jxxiaomei521</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
           <t>08/24 09:45:46</t>
         </is>
       </c>
-      <c r="B16" t="inlineStr">
+      <c r="B17" t="inlineStr">
         <is>
           <t>46380</t>
         </is>
       </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="D16" t="inlineStr">
+      <c r="C17" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
         <is>
           <t>jxxiaomei521</t>
         </is>
       </c>
-      <c r="E16" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-    </row>
-    <row r="17"/>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>总计</t>
-        </is>
-      </c>
-    </row>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="18"/>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>总入款</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>956000</t>
+          <t>总计</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>应下发</t>
+          <t>总入款</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>117225.8</t>
+          <t>956000</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>已下发</t>
+          <t>应下发</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>58649</t>
+          <t>117225.8</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
+          <t>已下发</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>70844</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
           <t>未下发</t>
         </is>
       </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>58576.8</t>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>46381.8</t>
         </is>
       </c>
     </row>

--- a/bills/JXZFSP01/-1003733706693/6d85008f7f7972fd90832a1022876df384976a1165aef80c1e3f256d2e720bdf/bill-all.xlsx
+++ b/bills/JXZFSP01/-1003733706693/6d85008f7f7972fd90832a1022876df384976a1165aef80c1e3f256d2e720bdf/bill-all.xlsx
@@ -75,12 +75,12 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>09/02 09:22:19</t>
+          <t>09/03 18:23:03</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>100000</t>
+          <t>50000</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -90,12 +90,12 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>8.2</t>
+          <t>8.4</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>12195.12</t>
+          <t>5952.38</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -105,7 +105,7 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>xinhui9</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -117,7 +117,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>08/25 11:41:35</t>
+          <t>09/02 09:22:19</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -132,12 +132,12 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>8.15</t>
+          <t>8.2</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>12269.94</t>
+          <t>12195.12</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -159,12 +159,12 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>08/24 08:22:11</t>
+          <t>08/25 11:41:35</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>378000</t>
+          <t>100000</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -179,7 +179,7 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>46380.37</t>
+          <t>12269.94</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -189,7 +189,7 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>xinhui9</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -201,166 +201,181 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
+          <t>08/24 08:22:11</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>378000</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>8.15</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>46380.37</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>tiantiananxin</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
           <t>08/24 08:03:39</t>
         </is>
       </c>
-      <c r="B8" t="inlineStr">
+      <c r="B9" t="inlineStr">
         <is>
           <t>378000</t>
         </is>
       </c>
-      <c r="C8" t="inlineStr">
+      <c r="C9" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
       </c>
-      <c r="D8" t="inlineStr">
+      <c r="D9" t="inlineStr">
         <is>
           <t>8.15</t>
         </is>
       </c>
-      <c r="E8" t="inlineStr">
+      <c r="E9" t="inlineStr">
         <is>
           <t>46380.37</t>
         </is>
       </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="G8" t="inlineStr">
+      <c r="F9" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
         <is>
           <t>xinhui9</t>
         </is>
       </c>
-      <c r="H8" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-    </row>
-    <row r="9"/>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>代付</t>
-        </is>
-      </c>
-    </row>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="10"/>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
+          <t>代付</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
           <t>时间</t>
         </is>
       </c>
-      <c r="B11" t="inlineStr">
+      <c r="B12" t="inlineStr">
         <is>
           <t>金额</t>
         </is>
       </c>
-      <c r="C11" t="inlineStr">
+      <c r="C12" t="inlineStr">
         <is>
           <t>费率</t>
         </is>
       </c>
-      <c r="D11" t="inlineStr">
+      <c r="D12" t="inlineStr">
         <is>
           <t>汇率</t>
         </is>
       </c>
-      <c r="E11" t="inlineStr">
+      <c r="E12" t="inlineStr">
         <is>
           <t>结算</t>
         </is>
       </c>
-      <c r="F11" t="inlineStr">
+      <c r="F12" t="inlineStr">
         <is>
           <t>标记人</t>
         </is>
       </c>
-      <c r="G11" t="inlineStr">
+      <c r="G12" t="inlineStr">
         <is>
           <t>操作人</t>
         </is>
       </c>
-      <c r="H11" t="inlineStr">
+      <c r="H12" t="inlineStr">
         <is>
           <t>备注</t>
         </is>
       </c>
     </row>
-    <row r="12"/>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>下发</t>
-        </is>
-      </c>
-    </row>
+    <row r="13"/>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>时间</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>金额</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>标记人</t>
-        </is>
-      </c>
-      <c r="D14" t="inlineStr">
-        <is>
-          <t>操作人</t>
-        </is>
-      </c>
-      <c r="E14" t="inlineStr">
-        <is>
-          <t>备注</t>
+          <t>下发</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>09/02 11:07:38</t>
+          <t>时间</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>12195</t>
+          <t>金额</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t/>
+          <t>标记人</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>操作人</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t/>
+          <t>备注</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>08/25 12:50:23</t>
+          <t>09/02 11:07:38</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>12269</t>
+          <t>12195</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -382,83 +397,110 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
+          <t>08/25 12:50:23</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>12269</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>jxxiaomei521</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
           <t>08/24 09:45:46</t>
         </is>
       </c>
-      <c r="B17" t="inlineStr">
+      <c r="B18" t="inlineStr">
         <is>
           <t>46380</t>
         </is>
       </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="D17" t="inlineStr">
+      <c r="C18" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
         <is>
           <t>jxxiaomei521</t>
         </is>
       </c>
-      <c r="E17" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-    </row>
-    <row r="18"/>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>总计</t>
-        </is>
-      </c>
-    </row>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="19"/>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>总入款</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>956000</t>
+          <t>总计</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>应下发</t>
+          <t>总入款</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>117225.8</t>
+          <t>1006000</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>已下发</t>
+          <t>应下发</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>70844</t>
+          <t>123178.18</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
+          <t>已下发</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>70844</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
           <t>未下发</t>
         </is>
       </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>46381.8</t>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>52334.18</t>
         </is>
       </c>
     </row>

--- a/bills/JXZFSP01/-1003733706693/6d85008f7f7972fd90832a1022876df384976a1165aef80c1e3f256d2e720bdf/bill-all.xlsx
+++ b/bills/JXZFSP01/-1003733706693/6d85008f7f7972fd90832a1022876df384976a1165aef80c1e3f256d2e720bdf/bill-all.xlsx
@@ -370,12 +370,12 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>09/02 11:07:38</t>
+          <t>09/03 18:23:33</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>12195</t>
+          <t>388</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -385,7 +385,7 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
@@ -397,12 +397,12 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>08/25 12:50:23</t>
+          <t>09/02 11:07:38</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>12269</t>
+          <t>12195</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -424,83 +424,110 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
+          <t>08/25 12:50:23</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>12269</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>jxxiaomei521</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
           <t>08/24 09:45:46</t>
         </is>
       </c>
-      <c r="B18" t="inlineStr">
+      <c r="B19" t="inlineStr">
         <is>
           <t>46380</t>
         </is>
       </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="D18" t="inlineStr">
+      <c r="C19" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
         <is>
           <t>jxxiaomei521</t>
         </is>
       </c>
-      <c r="E18" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-    </row>
-    <row r="19"/>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>总计</t>
-        </is>
-      </c>
-    </row>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="20"/>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>总入款</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>1006000</t>
+          <t>总计</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>应下发</t>
+          <t>总入款</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>123178.18</t>
+          <t>1006000</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>已下发</t>
+          <t>应下发</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>70844</t>
+          <t>123178.18</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
+          <t>已下发</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>71232</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
           <t>未下发</t>
         </is>
       </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>52334.18</t>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>51946.18</t>
         </is>
       </c>
     </row>

--- a/bills/JXZFSP01/-1003733706693/6d85008f7f7972fd90832a1022876df384976a1165aef80c1e3f256d2e720bdf/bill-all.xlsx
+++ b/bills/JXZFSP01/-1003733706693/6d85008f7f7972fd90832a1022876df384976a1165aef80c1e3f256d2e720bdf/bill-all.xlsx
@@ -370,12 +370,12 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>09/03 18:23:33</t>
+          <t>09/03 19:40:03</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>388</t>
+          <t>5564</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -385,7 +385,7 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>jxxiaomei521</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
@@ -397,12 +397,12 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>09/02 11:07:38</t>
+          <t>09/03 18:23:33</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>12195</t>
+          <t>388</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -412,7 +412,7 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
@@ -424,12 +424,12 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>08/25 12:50:23</t>
+          <t>09/02 11:07:38</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>12269</t>
+          <t>12195</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -451,83 +451,110 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
+          <t>08/25 12:50:23</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>12269</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>jxxiaomei521</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
           <t>08/24 09:45:46</t>
         </is>
       </c>
-      <c r="B19" t="inlineStr">
+      <c r="B20" t="inlineStr">
         <is>
           <t>46380</t>
         </is>
       </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="D19" t="inlineStr">
+      <c r="C20" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
         <is>
           <t>jxxiaomei521</t>
         </is>
       </c>
-      <c r="E19" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-    </row>
-    <row r="20"/>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>总计</t>
-        </is>
-      </c>
-    </row>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="21"/>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>总入款</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>1006000</t>
+          <t>总计</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>应下发</t>
+          <t>总入款</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>123178.18</t>
+          <t>1006000</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>已下发</t>
+          <t>应下发</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>71232</t>
+          <t>123178.18</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
+          <t>已下发</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>76796</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
           <t>未下发</t>
         </is>
       </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>51946.18</t>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>46382.18</t>
         </is>
       </c>
     </row>

--- a/bills/JXZFSP01/-1003733706693/6d85008f7f7972fd90832a1022876df384976a1165aef80c1e3f256d2e720bdf/bill-all.xlsx
+++ b/bills/JXZFSP01/-1003733706693/6d85008f7f7972fd90832a1022876df384976a1165aef80c1e3f256d2e720bdf/bill-all.xlsx
@@ -75,12 +75,12 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>09/03 18:23:03</t>
+          <t>09/04 19:57:09</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>50000</t>
+          <t>100000</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -90,12 +90,12 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>8.4</t>
+          <t>8.3</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>5952.38</t>
+          <t>12048.19</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -105,7 +105,7 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>xinhui9</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -117,12 +117,12 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>09/02 09:22:19</t>
+          <t>09/03 18:23:03</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>100000</t>
+          <t>50000</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -132,12 +132,12 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>8.2</t>
+          <t>8.4</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>12195.12</t>
+          <t>5952.38</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -147,7 +147,7 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>xinhui9</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -159,7 +159,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>08/25 11:41:35</t>
+          <t>09/02 09:22:19</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -174,12 +174,12 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>8.15</t>
+          <t>8.2</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>12269.94</t>
+          <t>12195.12</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -201,12 +201,12 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>08/24 08:22:11</t>
+          <t>08/25 11:41:35</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>378000</t>
+          <t>100000</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -221,7 +221,7 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>46380.37</t>
+          <t>12269.94</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -231,7 +231,7 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>xinhui9</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -243,166 +243,181 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
+          <t>08/24 08:22:11</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>378000</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>8.15</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>46380.37</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>tiantiananxin</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
           <t>08/24 08:03:39</t>
         </is>
       </c>
-      <c r="B9" t="inlineStr">
+      <c r="B10" t="inlineStr">
         <is>
           <t>378000</t>
         </is>
       </c>
-      <c r="C9" t="inlineStr">
+      <c r="C10" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
       </c>
-      <c r="D9" t="inlineStr">
+      <c r="D10" t="inlineStr">
         <is>
           <t>8.15</t>
         </is>
       </c>
-      <c r="E9" t="inlineStr">
+      <c r="E10" t="inlineStr">
         <is>
           <t>46380.37</t>
         </is>
       </c>
-      <c r="F9" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="G9" t="inlineStr">
+      <c r="F10" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
         <is>
           <t>xinhui9</t>
         </is>
       </c>
-      <c r="H9" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-    </row>
-    <row r="10"/>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>代付</t>
-        </is>
-      </c>
-    </row>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="11"/>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
+          <t>代付</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
           <t>时间</t>
         </is>
       </c>
-      <c r="B12" t="inlineStr">
+      <c r="B13" t="inlineStr">
         <is>
           <t>金额</t>
         </is>
       </c>
-      <c r="C12" t="inlineStr">
+      <c r="C13" t="inlineStr">
         <is>
           <t>费率</t>
         </is>
       </c>
-      <c r="D12" t="inlineStr">
+      <c r="D13" t="inlineStr">
         <is>
           <t>汇率</t>
         </is>
       </c>
-      <c r="E12" t="inlineStr">
+      <c r="E13" t="inlineStr">
         <is>
           <t>结算</t>
         </is>
       </c>
-      <c r="F12" t="inlineStr">
+      <c r="F13" t="inlineStr">
         <is>
           <t>标记人</t>
         </is>
       </c>
-      <c r="G12" t="inlineStr">
+      <c r="G13" t="inlineStr">
         <is>
           <t>操作人</t>
         </is>
       </c>
-      <c r="H12" t="inlineStr">
+      <c r="H13" t="inlineStr">
         <is>
           <t>备注</t>
         </is>
       </c>
     </row>
-    <row r="13"/>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>下发</t>
-        </is>
-      </c>
-    </row>
+    <row r="14"/>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>时间</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>金额</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>标记人</t>
-        </is>
-      </c>
-      <c r="D15" t="inlineStr">
-        <is>
-          <t>操作人</t>
-        </is>
-      </c>
-      <c r="E15" t="inlineStr">
-        <is>
-          <t>备注</t>
+          <t>下发</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>09/03 19:40:03</t>
+          <t>时间</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>5564</t>
+          <t>金额</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t/>
+          <t>标记人</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>操作人</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t/>
+          <t>备注</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>09/03 18:23:33</t>
+          <t>09/03 19:40:03</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>388</t>
+          <t>5564</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -412,7 +427,7 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>jxxiaomei521</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
@@ -424,12 +439,12 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>09/02 11:07:38</t>
+          <t>09/03 18:23:33</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>12195</t>
+          <t>388</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -439,7 +454,7 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
@@ -451,12 +466,12 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>08/25 12:50:23</t>
+          <t>09/02 11:07:38</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>12269</t>
+          <t>12195</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -478,83 +493,110 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
+          <t>08/25 12:50:23</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>12269</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>jxxiaomei521</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
           <t>08/24 09:45:46</t>
         </is>
       </c>
-      <c r="B20" t="inlineStr">
+      <c r="B21" t="inlineStr">
         <is>
           <t>46380</t>
         </is>
       </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="D20" t="inlineStr">
+      <c r="C21" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
         <is>
           <t>jxxiaomei521</t>
         </is>
       </c>
-      <c r="E20" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-    </row>
-    <row r="21"/>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>总计</t>
-        </is>
-      </c>
-    </row>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="22"/>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>总入款</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>1006000</t>
+          <t>总计</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>应下发</t>
+          <t>总入款</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>123178.18</t>
+          <t>1106000</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>已下发</t>
+          <t>应下发</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>76796</t>
+          <t>135226.37</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
+          <t>已下发</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>76796</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
           <t>未下发</t>
         </is>
       </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>46382.18</t>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>58430.37</t>
         </is>
       </c>
     </row>

--- a/bills/JXZFSP01/-1003733706693/6d85008f7f7972fd90832a1022876df384976a1165aef80c1e3f256d2e720bdf/bill-all.xlsx
+++ b/bills/JXZFSP01/-1003733706693/6d85008f7f7972fd90832a1022876df384976a1165aef80c1e3f256d2e720bdf/bill-all.xlsx
@@ -412,12 +412,12 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>09/03 19:40:03</t>
+          <t>09/04 19:57:15</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>5564</t>
+          <t>288</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -427,7 +427,7 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>xinhui9</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
@@ -439,12 +439,12 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>09/03 18:23:33</t>
+          <t>09/03 19:40:03</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>388</t>
+          <t>5564</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -454,7 +454,7 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>jxxiaomei521</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
@@ -466,12 +466,12 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>09/02 11:07:38</t>
+          <t>09/03 18:23:33</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>12195</t>
+          <t>388</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -481,7 +481,7 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
@@ -493,12 +493,12 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>08/25 12:50:23</t>
+          <t>09/02 11:07:38</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>12269</t>
+          <t>12195</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -520,83 +520,110 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
+          <t>08/25 12:50:23</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>12269</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>jxxiaomei521</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
           <t>08/24 09:45:46</t>
         </is>
       </c>
-      <c r="B21" t="inlineStr">
+      <c r="B22" t="inlineStr">
         <is>
           <t>46380</t>
         </is>
       </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="D21" t="inlineStr">
+      <c r="C22" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
         <is>
           <t>jxxiaomei521</t>
         </is>
       </c>
-      <c r="E21" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-    </row>
-    <row r="22"/>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>总计</t>
-        </is>
-      </c>
-    </row>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="23"/>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>总入款</t>
-        </is>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>1106000</t>
+          <t>总计</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>应下发</t>
+          <t>总入款</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>135226.37</t>
+          <t>1106000</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>已下发</t>
+          <t>应下发</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>76796</t>
+          <t>135226.37</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
+          <t>已下发</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>77084</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
           <t>未下发</t>
         </is>
       </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>58430.37</t>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>58142.37</t>
         </is>
       </c>
     </row>

--- a/bills/JXZFSP01/-1003733706693/6d85008f7f7972fd90832a1022876df384976a1165aef80c1e3f256d2e720bdf/bill-all.xlsx
+++ b/bills/JXZFSP01/-1003733706693/6d85008f7f7972fd90832a1022876df384976a1165aef80c1e3f256d2e720bdf/bill-all.xlsx
@@ -412,12 +412,12 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>09/04 19:57:15</t>
+          <t>09/04 20:59:45</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>288</t>
+          <t>11760</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -427,7 +427,7 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>xinhui9</t>
+          <t>jxxiaomei521</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
@@ -439,12 +439,12 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>09/03 19:40:03</t>
+          <t>09/04 19:57:15</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>5564</t>
+          <t>288</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -454,7 +454,7 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>xinhui9</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
@@ -466,12 +466,12 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>09/03 18:23:33</t>
+          <t>09/03 19:40:03</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>388</t>
+          <t>5564</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -481,7 +481,7 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>jxxiaomei521</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
@@ -493,12 +493,12 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>09/02 11:07:38</t>
+          <t>09/03 18:23:33</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>12195</t>
+          <t>388</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -508,7 +508,7 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
@@ -520,12 +520,12 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>08/25 12:50:23</t>
+          <t>09/02 11:07:38</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>12269</t>
+          <t>12195</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -547,83 +547,110 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
+          <t>08/25 12:50:23</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>12269</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>jxxiaomei521</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
           <t>08/24 09:45:46</t>
         </is>
       </c>
-      <c r="B22" t="inlineStr">
+      <c r="B23" t="inlineStr">
         <is>
           <t>46380</t>
         </is>
       </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="D22" t="inlineStr">
+      <c r="C23" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
         <is>
           <t>jxxiaomei521</t>
         </is>
       </c>
-      <c r="E22" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-    </row>
-    <row r="23"/>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>总计</t>
-        </is>
-      </c>
-    </row>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="24"/>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>总入款</t>
-        </is>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>1106000</t>
+          <t>总计</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>应下发</t>
+          <t>总入款</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>135226.37</t>
+          <t>1106000</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>已下发</t>
+          <t>应下发</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>77084</t>
+          <t>135226.37</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
+          <t>已下发</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>88844</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
           <t>未下发</t>
         </is>
       </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>58142.37</t>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>46382.37</t>
         </is>
       </c>
     </row>

--- a/bills/JXZFSP01/-1003733706693/6d85008f7f7972fd90832a1022876df384976a1165aef80c1e3f256d2e720bdf/bill-all.xlsx
+++ b/bills/JXZFSP01/-1003733706693/6d85008f7f7972fd90832a1022876df384976a1165aef80c1e3f256d2e720bdf/bill-all.xlsx
@@ -75,7 +75,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>09/04 19:57:09</t>
+          <t>09/07 17:02:49</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -90,12 +90,12 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>8.3</t>
+          <t>8.4</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>12048.19</t>
+          <t>11904.76</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -117,12 +117,12 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>09/03 18:23:03</t>
+          <t>09/04 19:57:09</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>50000</t>
+          <t>100000</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -132,12 +132,12 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>8.4</t>
+          <t>8.3</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>5952.38</t>
+          <t>12048.19</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -147,7 +147,7 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>xinhui9</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -159,12 +159,12 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>09/02 09:22:19</t>
+          <t>09/03 18:23:03</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>100000</t>
+          <t>50000</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -174,12 +174,12 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>8.2</t>
+          <t>8.4</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>12195.12</t>
+          <t>5952.38</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -189,7 +189,7 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>xinhui9</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -201,7 +201,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>08/25 11:41:35</t>
+          <t>09/02 09:22:19</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -216,12 +216,12 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>8.15</t>
+          <t>8.2</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>12269.94</t>
+          <t>12195.12</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -243,12 +243,12 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>08/24 08:22:11</t>
+          <t>08/25 11:41:35</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>378000</t>
+          <t>100000</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -263,7 +263,7 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>46380.37</t>
+          <t>12269.94</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -273,7 +273,7 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>xinhui9</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -285,166 +285,181 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
+          <t>08/24 08:22:11</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>378000</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>8.15</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>46380.37</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>tiantiananxin</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
           <t>08/24 08:03:39</t>
         </is>
       </c>
-      <c r="B10" t="inlineStr">
+      <c r="B11" t="inlineStr">
         <is>
           <t>378000</t>
         </is>
       </c>
-      <c r="C10" t="inlineStr">
+      <c r="C11" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
       </c>
-      <c r="D10" t="inlineStr">
+      <c r="D11" t="inlineStr">
         <is>
           <t>8.15</t>
         </is>
       </c>
-      <c r="E10" t="inlineStr">
+      <c r="E11" t="inlineStr">
         <is>
           <t>46380.37</t>
         </is>
       </c>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="G10" t="inlineStr">
+      <c r="F11" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
         <is>
           <t>xinhui9</t>
         </is>
       </c>
-      <c r="H10" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-    </row>
-    <row r="11"/>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>代付</t>
-        </is>
-      </c>
-    </row>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="12"/>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
+          <t>代付</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
           <t>时间</t>
         </is>
       </c>
-      <c r="B13" t="inlineStr">
+      <c r="B14" t="inlineStr">
         <is>
           <t>金额</t>
         </is>
       </c>
-      <c r="C13" t="inlineStr">
+      <c r="C14" t="inlineStr">
         <is>
           <t>费率</t>
         </is>
       </c>
-      <c r="D13" t="inlineStr">
+      <c r="D14" t="inlineStr">
         <is>
           <t>汇率</t>
         </is>
       </c>
-      <c r="E13" t="inlineStr">
+      <c r="E14" t="inlineStr">
         <is>
           <t>结算</t>
         </is>
       </c>
-      <c r="F13" t="inlineStr">
+      <c r="F14" t="inlineStr">
         <is>
           <t>标记人</t>
         </is>
       </c>
-      <c r="G13" t="inlineStr">
+      <c r="G14" t="inlineStr">
         <is>
           <t>操作人</t>
         </is>
       </c>
-      <c r="H13" t="inlineStr">
+      <c r="H14" t="inlineStr">
         <is>
           <t>备注</t>
         </is>
       </c>
     </row>
-    <row r="14"/>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>下发</t>
-        </is>
-      </c>
-    </row>
+    <row r="15"/>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>时间</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>金额</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>标记人</t>
-        </is>
-      </c>
-      <c r="D16" t="inlineStr">
-        <is>
-          <t>操作人</t>
-        </is>
-      </c>
-      <c r="E16" t="inlineStr">
-        <is>
-          <t>备注</t>
+          <t>下发</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>09/04 20:59:45</t>
+          <t>时间</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>11760</t>
+          <t>金额</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t/>
+          <t>标记人</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>操作人</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t/>
+          <t>备注</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>09/04 19:57:15</t>
+          <t>09/04 20:59:45</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>288</t>
+          <t>11760</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -454,7 +469,7 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>xinhui9</t>
+          <t>jxxiaomei521</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
@@ -466,12 +481,12 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>09/03 19:40:03</t>
+          <t>09/04 19:57:15</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>5564</t>
+          <t>288</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -481,7 +496,7 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>xinhui9</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
@@ -493,12 +508,12 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>09/03 18:23:33</t>
+          <t>09/03 19:40:03</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>388</t>
+          <t>5564</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -508,7 +523,7 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>jxxiaomei521</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
@@ -520,12 +535,12 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>09/02 11:07:38</t>
+          <t>09/03 18:23:33</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>12195</t>
+          <t>388</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -535,7 +550,7 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
@@ -547,12 +562,12 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>08/25 12:50:23</t>
+          <t>09/02 11:07:38</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>12269</t>
+          <t>12195</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -574,83 +589,110 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
+          <t>08/25 12:50:23</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>12269</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>jxxiaomei521</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
           <t>08/24 09:45:46</t>
         </is>
       </c>
-      <c r="B23" t="inlineStr">
+      <c r="B24" t="inlineStr">
         <is>
           <t>46380</t>
         </is>
       </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="D23" t="inlineStr">
+      <c r="C24" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
         <is>
           <t>jxxiaomei521</t>
         </is>
       </c>
-      <c r="E23" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-    </row>
-    <row r="24"/>
-    <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>总计</t>
-        </is>
-      </c>
-    </row>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="25"/>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>总入款</t>
-        </is>
-      </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>1106000</t>
+          <t>总计</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>应下发</t>
+          <t>总入款</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>135226.37</t>
+          <t>1206000</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>已下发</t>
+          <t>应下发</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>88844</t>
+          <t>147131.13</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
+          <t>已下发</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>88844</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
           <t>未下发</t>
         </is>
       </c>
-      <c r="B29" t="inlineStr">
-        <is>
-          <t>46382.37</t>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>58287.13</t>
         </is>
       </c>
     </row>

--- a/bills/JXZFSP01/-1003733706693/6d85008f7f7972fd90832a1022876df384976a1165aef80c1e3f256d2e720bdf/bill-all.xlsx
+++ b/bills/JXZFSP01/-1003733706693/6d85008f7f7972fd90832a1022876df384976a1165aef80c1e3f256d2e720bdf/bill-all.xlsx
@@ -454,12 +454,12 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>09/04 20:59:45</t>
+          <t>09/07 19:03:29</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>11760</t>
+          <t>11904</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -481,12 +481,12 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>09/04 19:57:15</t>
+          <t>09/04 20:59:45</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>288</t>
+          <t>11760</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -496,7 +496,7 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>xinhui9</t>
+          <t>jxxiaomei521</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
@@ -508,12 +508,12 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>09/03 19:40:03</t>
+          <t>09/04 19:57:15</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>5564</t>
+          <t>288</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -523,7 +523,7 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>xinhui9</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
@@ -535,12 +535,12 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>09/03 18:23:33</t>
+          <t>09/03 19:40:03</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>388</t>
+          <t>5564</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -550,7 +550,7 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>jxxiaomei521</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
@@ -562,12 +562,12 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>09/02 11:07:38</t>
+          <t>09/03 18:23:33</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>12195</t>
+          <t>388</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -577,7 +577,7 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
@@ -589,12 +589,12 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>08/25 12:50:23</t>
+          <t>09/02 11:07:38</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>12269</t>
+          <t>12195</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -616,83 +616,110 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
+          <t>08/25 12:50:23</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>12269</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>jxxiaomei521</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
           <t>08/24 09:45:46</t>
         </is>
       </c>
-      <c r="B24" t="inlineStr">
+      <c r="B25" t="inlineStr">
         <is>
           <t>46380</t>
         </is>
       </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="D24" t="inlineStr">
+      <c r="C25" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
         <is>
           <t>jxxiaomei521</t>
         </is>
       </c>
-      <c r="E24" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-    </row>
-    <row r="25"/>
-    <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>总计</t>
-        </is>
-      </c>
-    </row>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="26"/>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>总入款</t>
-        </is>
-      </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>1206000</t>
+          <t>总计</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>应下发</t>
+          <t>总入款</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>147131.13</t>
+          <t>1206000</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>已下发</t>
+          <t>应下发</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>88844</t>
+          <t>147131.13</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
+          <t>已下发</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>100748</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
           <t>未下发</t>
         </is>
       </c>
-      <c r="B30" t="inlineStr">
-        <is>
-          <t>58287.13</t>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>46383.13</t>
         </is>
       </c>
     </row>

--- a/bills/JXZFSP01/-1003733706693/6d85008f7f7972fd90832a1022876df384976a1165aef80c1e3f256d2e720bdf/bill-all.xlsx
+++ b/bills/JXZFSP01/-1003733706693/6d85008f7f7972fd90832a1022876df384976a1165aef80c1e3f256d2e720bdf/bill-all.xlsx
@@ -75,12 +75,12 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>09/07 17:02:49</t>
+          <t>09/08 13:38:20</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>100000</t>
+          <t>150000</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -90,12 +90,12 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>8.4</t>
+          <t>8.25</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>11904.76</t>
+          <t>18181.82</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -117,7 +117,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>09/04 19:57:09</t>
+          <t>09/07 17:02:49</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -132,12 +132,12 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>8.3</t>
+          <t>8.4</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>12048.19</t>
+          <t>11904.76</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -159,12 +159,12 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>09/03 18:23:03</t>
+          <t>09/04 19:57:09</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>50000</t>
+          <t>100000</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -174,12 +174,12 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>8.4</t>
+          <t>8.3</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>5952.38</t>
+          <t>12048.19</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -189,7 +189,7 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>xinhui9</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -201,12 +201,12 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>09/02 09:22:19</t>
+          <t>09/03 18:23:03</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>100000</t>
+          <t>50000</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -216,12 +216,12 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>8.2</t>
+          <t>8.4</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>12195.12</t>
+          <t>5952.38</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -231,7 +231,7 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>xinhui9</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -243,7 +243,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>08/25 11:41:35</t>
+          <t>09/02 09:22:19</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -258,12 +258,12 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>8.15</t>
+          <t>8.2</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>12269.94</t>
+          <t>12195.12</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -285,12 +285,12 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>08/24 08:22:11</t>
+          <t>08/25 11:41:35</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>378000</t>
+          <t>100000</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -305,7 +305,7 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>46380.37</t>
+          <t>12269.94</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -315,7 +315,7 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>xinhui9</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -327,166 +327,181 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
+          <t>08/24 08:22:11</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>378000</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>8.15</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>46380.37</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>tiantiananxin</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
           <t>08/24 08:03:39</t>
         </is>
       </c>
-      <c r="B11" t="inlineStr">
+      <c r="B12" t="inlineStr">
         <is>
           <t>378000</t>
         </is>
       </c>
-      <c r="C11" t="inlineStr">
+      <c r="C12" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
       </c>
-      <c r="D11" t="inlineStr">
+      <c r="D12" t="inlineStr">
         <is>
           <t>8.15</t>
         </is>
       </c>
-      <c r="E11" t="inlineStr">
+      <c r="E12" t="inlineStr">
         <is>
           <t>46380.37</t>
         </is>
       </c>
-      <c r="F11" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="G11" t="inlineStr">
+      <c r="F12" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
         <is>
           <t>xinhui9</t>
         </is>
       </c>
-      <c r="H11" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-    </row>
-    <row r="12"/>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>代付</t>
-        </is>
-      </c>
-    </row>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="13"/>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
+          <t>代付</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
           <t>时间</t>
         </is>
       </c>
-      <c r="B14" t="inlineStr">
+      <c r="B15" t="inlineStr">
         <is>
           <t>金额</t>
         </is>
       </c>
-      <c r="C14" t="inlineStr">
+      <c r="C15" t="inlineStr">
         <is>
           <t>费率</t>
         </is>
       </c>
-      <c r="D14" t="inlineStr">
+      <c r="D15" t="inlineStr">
         <is>
           <t>汇率</t>
         </is>
       </c>
-      <c r="E14" t="inlineStr">
+      <c r="E15" t="inlineStr">
         <is>
           <t>结算</t>
         </is>
       </c>
-      <c r="F14" t="inlineStr">
+      <c r="F15" t="inlineStr">
         <is>
           <t>标记人</t>
         </is>
       </c>
-      <c r="G14" t="inlineStr">
+      <c r="G15" t="inlineStr">
         <is>
           <t>操作人</t>
         </is>
       </c>
-      <c r="H14" t="inlineStr">
+      <c r="H15" t="inlineStr">
         <is>
           <t>备注</t>
         </is>
       </c>
     </row>
-    <row r="15"/>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>下发</t>
-        </is>
-      </c>
-    </row>
+    <row r="16"/>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>时间</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>金额</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>标记人</t>
-        </is>
-      </c>
-      <c r="D17" t="inlineStr">
-        <is>
-          <t>操作人</t>
-        </is>
-      </c>
-      <c r="E17" t="inlineStr">
-        <is>
-          <t>备注</t>
+          <t>下发</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>09/07 19:03:29</t>
+          <t>时间</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>11904</t>
+          <t>金额</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t/>
+          <t>标记人</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>操作人</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t/>
+          <t>备注</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>09/04 20:59:45</t>
+          <t>09/07 19:03:29</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>11760</t>
+          <t>11904</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -508,12 +523,12 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>09/04 19:57:15</t>
+          <t>09/04 20:59:45</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>288</t>
+          <t>11760</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -523,7 +538,7 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>xinhui9</t>
+          <t>jxxiaomei521</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
@@ -535,12 +550,12 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>09/03 19:40:03</t>
+          <t>09/04 19:57:15</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>5564</t>
+          <t>288</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -550,7 +565,7 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>xinhui9</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
@@ -562,12 +577,12 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>09/03 18:23:33</t>
+          <t>09/03 19:40:03</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>388</t>
+          <t>5564</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -577,7 +592,7 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>jxxiaomei521</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
@@ -589,12 +604,12 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>09/02 11:07:38</t>
+          <t>09/03 18:23:33</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>12195</t>
+          <t>388</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -604,7 +619,7 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
@@ -616,12 +631,12 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>08/25 12:50:23</t>
+          <t>09/02 11:07:38</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>12269</t>
+          <t>12195</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -643,83 +658,110 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
+          <t>08/25 12:50:23</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>12269</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>jxxiaomei521</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
           <t>08/24 09:45:46</t>
         </is>
       </c>
-      <c r="B25" t="inlineStr">
+      <c r="B26" t="inlineStr">
         <is>
           <t>46380</t>
         </is>
       </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="D25" t="inlineStr">
+      <c r="C26" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
         <is>
           <t>jxxiaomei521</t>
         </is>
       </c>
-      <c r="E25" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-    </row>
-    <row r="26"/>
-    <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>总计</t>
-        </is>
-      </c>
-    </row>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="27"/>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>总入款</t>
-        </is>
-      </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>1206000</t>
+          <t>总计</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>应下发</t>
+          <t>总入款</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>147131.13</t>
+          <t>1356000</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>已下发</t>
+          <t>应下发</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>100748</t>
+          <t>165312.95</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
+          <t>已下发</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>100748</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
           <t>未下发</t>
         </is>
       </c>
-      <c r="B31" t="inlineStr">
-        <is>
-          <t>46383.13</t>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>64564.95</t>
         </is>
       </c>
     </row>

--- a/bills/JXZFSP01/-1003733706693/6d85008f7f7972fd90832a1022876df384976a1165aef80c1e3f256d2e720bdf/bill-all.xlsx
+++ b/bills/JXZFSP01/-1003733706693/6d85008f7f7972fd90832a1022876df384976a1165aef80c1e3f256d2e720bdf/bill-all.xlsx
@@ -496,12 +496,12 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>09/07 19:03:29</t>
+          <t>09/08 15:27:46</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>11904</t>
+          <t>18181</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -523,12 +523,12 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>09/04 20:59:45</t>
+          <t>09/07 19:03:29</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>11760</t>
+          <t>11904</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -550,12 +550,12 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>09/04 19:57:15</t>
+          <t>09/04 20:59:45</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>288</t>
+          <t>11760</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -565,7 +565,7 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>xinhui9</t>
+          <t>jxxiaomei521</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
@@ -577,12 +577,12 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>09/03 19:40:03</t>
+          <t>09/04 19:57:15</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>5564</t>
+          <t>288</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -592,7 +592,7 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>xinhui9</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
@@ -604,12 +604,12 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>09/03 18:23:33</t>
+          <t>09/03 19:40:03</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>388</t>
+          <t>5564</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -619,7 +619,7 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>jxxiaomei521</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
@@ -631,12 +631,12 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>09/02 11:07:38</t>
+          <t>09/03 18:23:33</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>12195</t>
+          <t>388</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -646,7 +646,7 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
@@ -658,12 +658,12 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>08/25 12:50:23</t>
+          <t>09/02 11:07:38</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>12269</t>
+          <t>12195</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -685,83 +685,110 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
+          <t>08/25 12:50:23</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>12269</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>jxxiaomei521</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
           <t>08/24 09:45:46</t>
         </is>
       </c>
-      <c r="B26" t="inlineStr">
+      <c r="B27" t="inlineStr">
         <is>
           <t>46380</t>
         </is>
       </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="D26" t="inlineStr">
+      <c r="C27" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
         <is>
           <t>jxxiaomei521</t>
         </is>
       </c>
-      <c r="E26" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-    </row>
-    <row r="27"/>
-    <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>总计</t>
-        </is>
-      </c>
-    </row>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="28"/>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>总入款</t>
-        </is>
-      </c>
-      <c r="B29" t="inlineStr">
-        <is>
-          <t>1356000</t>
+          <t>总计</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>应下发</t>
+          <t>总入款</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>165312.95</t>
+          <t>1356000</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>已下发</t>
+          <t>应下发</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>100748</t>
+          <t>165312.95</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
+          <t>已下发</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>118929</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
           <t>未下发</t>
         </is>
       </c>
-      <c r="B32" t="inlineStr">
-        <is>
-          <t>64564.95</t>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>46383.95</t>
         </is>
       </c>
     </row>

--- a/bills/JXZFSP01/-1003733706693/6d85008f7f7972fd90832a1022876df384976a1165aef80c1e3f256d2e720bdf/bill-all.xlsx
+++ b/bills/JXZFSP01/-1003733706693/6d85008f7f7972fd90832a1022876df384976a1165aef80c1e3f256d2e720bdf/bill-all.xlsx
@@ -75,12 +75,12 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>09/08 13:38:20</t>
+          <t>09/09 12:13:06</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>150000</t>
+          <t>79800</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -90,12 +90,12 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>8.25</t>
+          <t>8.5</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>18181.82</t>
+          <t>9388.24</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -117,12 +117,12 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>09/07 17:02:49</t>
+          <t>09/08 13:38:20</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>100000</t>
+          <t>150000</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -132,12 +132,12 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>8.4</t>
+          <t>8.25</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>11904.76</t>
+          <t>18181.82</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -159,7 +159,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>09/04 19:57:09</t>
+          <t>09/07 17:02:49</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -174,12 +174,12 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>8.3</t>
+          <t>8.4</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>12048.19</t>
+          <t>11904.76</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -201,12 +201,12 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>09/03 18:23:03</t>
+          <t>09/04 19:57:09</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>50000</t>
+          <t>100000</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -216,12 +216,12 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>8.4</t>
+          <t>8.3</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>5952.38</t>
+          <t>12048.19</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -231,7 +231,7 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>xinhui9</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -243,12 +243,12 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>09/02 09:22:19</t>
+          <t>09/03 18:23:03</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>100000</t>
+          <t>50000</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -258,12 +258,12 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>8.2</t>
+          <t>8.4</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>12195.12</t>
+          <t>5952.38</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -273,7 +273,7 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>xinhui9</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -285,7 +285,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>08/25 11:41:35</t>
+          <t>09/02 09:22:19</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -300,12 +300,12 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>8.15</t>
+          <t>8.2</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>12269.94</t>
+          <t>12195.12</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -327,12 +327,12 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>08/24 08:22:11</t>
+          <t>08/25 11:41:35</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>378000</t>
+          <t>100000</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -347,7 +347,7 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>46380.37</t>
+          <t>12269.94</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -357,7 +357,7 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>xinhui9</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -369,166 +369,181 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
+          <t>08/24 08:22:11</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>378000</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>8.15</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>46380.37</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>tiantiananxin</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
           <t>08/24 08:03:39</t>
         </is>
       </c>
-      <c r="B12" t="inlineStr">
+      <c r="B13" t="inlineStr">
         <is>
           <t>378000</t>
         </is>
       </c>
-      <c r="C12" t="inlineStr">
+      <c r="C13" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
       </c>
-      <c r="D12" t="inlineStr">
+      <c r="D13" t="inlineStr">
         <is>
           <t>8.15</t>
         </is>
       </c>
-      <c r="E12" t="inlineStr">
+      <c r="E13" t="inlineStr">
         <is>
           <t>46380.37</t>
         </is>
       </c>
-      <c r="F12" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="G12" t="inlineStr">
+      <c r="F13" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
         <is>
           <t>xinhui9</t>
         </is>
       </c>
-      <c r="H12" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-    </row>
-    <row r="13"/>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>代付</t>
-        </is>
-      </c>
-    </row>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="14"/>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
+          <t>代付</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
           <t>时间</t>
         </is>
       </c>
-      <c r="B15" t="inlineStr">
+      <c r="B16" t="inlineStr">
         <is>
           <t>金额</t>
         </is>
       </c>
-      <c r="C15" t="inlineStr">
+      <c r="C16" t="inlineStr">
         <is>
           <t>费率</t>
         </is>
       </c>
-      <c r="D15" t="inlineStr">
+      <c r="D16" t="inlineStr">
         <is>
           <t>汇率</t>
         </is>
       </c>
-      <c r="E15" t="inlineStr">
+      <c r="E16" t="inlineStr">
         <is>
           <t>结算</t>
         </is>
       </c>
-      <c r="F15" t="inlineStr">
+      <c r="F16" t="inlineStr">
         <is>
           <t>标记人</t>
         </is>
       </c>
-      <c r="G15" t="inlineStr">
+      <c r="G16" t="inlineStr">
         <is>
           <t>操作人</t>
         </is>
       </c>
-      <c r="H15" t="inlineStr">
+      <c r="H16" t="inlineStr">
         <is>
           <t>备注</t>
         </is>
       </c>
     </row>
-    <row r="16"/>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>下发</t>
-        </is>
-      </c>
-    </row>
+    <row r="17"/>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>时间</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>金额</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>标记人</t>
-        </is>
-      </c>
-      <c r="D18" t="inlineStr">
-        <is>
-          <t>操作人</t>
-        </is>
-      </c>
-      <c r="E18" t="inlineStr">
-        <is>
-          <t>备注</t>
+          <t>下发</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>09/08 15:27:46</t>
+          <t>时间</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>18181</t>
+          <t>金额</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t/>
+          <t>标记人</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>操作人</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t/>
+          <t>备注</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>09/07 19:03:29</t>
+          <t>09/08 15:27:46</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>11904</t>
+          <t>18181</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -550,12 +565,12 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>09/04 20:59:45</t>
+          <t>09/07 19:03:29</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>11760</t>
+          <t>11904</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -577,12 +592,12 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>09/04 19:57:15</t>
+          <t>09/04 20:59:45</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>288</t>
+          <t>11760</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -592,7 +607,7 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>xinhui9</t>
+          <t>jxxiaomei521</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
@@ -604,12 +619,12 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>09/03 19:40:03</t>
+          <t>09/04 19:57:15</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>5564</t>
+          <t>288</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -619,7 +634,7 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>xinhui9</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
@@ -631,12 +646,12 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>09/03 18:23:33</t>
+          <t>09/03 19:40:03</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>388</t>
+          <t>5564</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -646,7 +661,7 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>jxxiaomei521</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
@@ -658,12 +673,12 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>09/02 11:07:38</t>
+          <t>09/03 18:23:33</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>12195</t>
+          <t>388</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -673,7 +688,7 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
@@ -685,12 +700,12 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>08/25 12:50:23</t>
+          <t>09/02 11:07:38</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>12269</t>
+          <t>12195</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -712,83 +727,110 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
+          <t>08/25 12:50:23</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>12269</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>jxxiaomei521</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
           <t>08/24 09:45:46</t>
         </is>
       </c>
-      <c r="B27" t="inlineStr">
+      <c r="B28" t="inlineStr">
         <is>
           <t>46380</t>
         </is>
       </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="D27" t="inlineStr">
+      <c r="C28" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
         <is>
           <t>jxxiaomei521</t>
         </is>
       </c>
-      <c r="E27" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-    </row>
-    <row r="28"/>
-    <row r="29">
-      <c r="A29" t="inlineStr">
-        <is>
-          <t>总计</t>
-        </is>
-      </c>
-    </row>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="29"/>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>总入款</t>
-        </is>
-      </c>
-      <c r="B30" t="inlineStr">
-        <is>
-          <t>1356000</t>
+          <t>总计</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>应下发</t>
+          <t>总入款</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>165312.95</t>
+          <t>1435800</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>已下发</t>
+          <t>应下发</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>118929</t>
+          <t>174701.19</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
+          <t>已下发</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>118929</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
           <t>未下发</t>
         </is>
       </c>
-      <c r="B33" t="inlineStr">
-        <is>
-          <t>46383.95</t>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>55772.19</t>
         </is>
       </c>
     </row>

--- a/bills/JXZFSP01/-1003733706693/6d85008f7f7972fd90832a1022876df384976a1165aef80c1e3f256d2e720bdf/bill-all.xlsx
+++ b/bills/JXZFSP01/-1003733706693/6d85008f7f7972fd90832a1022876df384976a1165aef80c1e3f256d2e720bdf/bill-all.xlsx
@@ -75,12 +75,12 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>09/09 12:13:06</t>
+          <t>09/09 14:13:29</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>79800</t>
+          <t>110000</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -90,12 +90,12 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>8.5</t>
+          <t>8.4</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>9388.24</t>
+          <t>13095.24</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -117,12 +117,12 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>09/08 13:38:20</t>
+          <t>09/09 12:13:06</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>150000</t>
+          <t>79800</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -132,12 +132,12 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>8.25</t>
+          <t>8.5</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>18181.82</t>
+          <t>9388.24</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -159,12 +159,12 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>09/07 17:02:49</t>
+          <t>09/08 13:38:20</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>100000</t>
+          <t>150000</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -174,12 +174,12 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>8.4</t>
+          <t>8.25</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>11904.76</t>
+          <t>18181.82</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -201,7 +201,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>09/04 19:57:09</t>
+          <t>09/07 17:02:49</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -216,12 +216,12 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>8.3</t>
+          <t>8.4</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>12048.19</t>
+          <t>11904.76</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -243,12 +243,12 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>09/03 18:23:03</t>
+          <t>09/04 19:57:09</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>50000</t>
+          <t>100000</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -258,12 +258,12 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>8.4</t>
+          <t>8.3</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>5952.38</t>
+          <t>12048.19</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -273,7 +273,7 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>xinhui9</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -285,12 +285,12 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>09/02 09:22:19</t>
+          <t>09/03 18:23:03</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>100000</t>
+          <t>50000</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -300,12 +300,12 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>8.2</t>
+          <t>8.4</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>12195.12</t>
+          <t>5952.38</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -315,7 +315,7 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>xinhui9</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -327,7 +327,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>08/25 11:41:35</t>
+          <t>09/02 09:22:19</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -342,12 +342,12 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>8.15</t>
+          <t>8.2</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>12269.94</t>
+          <t>12195.12</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -369,12 +369,12 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>08/24 08:22:11</t>
+          <t>08/25 11:41:35</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>378000</t>
+          <t>100000</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -389,7 +389,7 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>46380.37</t>
+          <t>12269.94</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -399,7 +399,7 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>xinhui9</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
@@ -411,166 +411,181 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
+          <t>08/24 08:22:11</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>378000</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>8.15</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>46380.37</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>tiantiananxin</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
           <t>08/24 08:03:39</t>
         </is>
       </c>
-      <c r="B13" t="inlineStr">
+      <c r="B14" t="inlineStr">
         <is>
           <t>378000</t>
         </is>
       </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="D13" t="inlineStr">
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
         <is>
           <t>8.15</t>
         </is>
       </c>
-      <c r="E13" t="inlineStr">
+      <c r="E14" t="inlineStr">
         <is>
           <t>46380.37</t>
         </is>
       </c>
-      <c r="F13" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="G13" t="inlineStr">
+      <c r="F14" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
         <is>
           <t>xinhui9</t>
         </is>
       </c>
-      <c r="H13" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-    </row>
-    <row r="14"/>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>代付</t>
-        </is>
-      </c>
-    </row>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="15"/>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
+          <t>代付</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
           <t>时间</t>
         </is>
       </c>
-      <c r="B16" t="inlineStr">
+      <c r="B17" t="inlineStr">
         <is>
           <t>金额</t>
         </is>
       </c>
-      <c r="C16" t="inlineStr">
+      <c r="C17" t="inlineStr">
         <is>
           <t>费率</t>
         </is>
       </c>
-      <c r="D16" t="inlineStr">
+      <c r="D17" t="inlineStr">
         <is>
           <t>汇率</t>
         </is>
       </c>
-      <c r="E16" t="inlineStr">
+      <c r="E17" t="inlineStr">
         <is>
           <t>结算</t>
         </is>
       </c>
-      <c r="F16" t="inlineStr">
+      <c r="F17" t="inlineStr">
         <is>
           <t>标记人</t>
         </is>
       </c>
-      <c r="G16" t="inlineStr">
+      <c r="G17" t="inlineStr">
         <is>
           <t>操作人</t>
         </is>
       </c>
-      <c r="H16" t="inlineStr">
+      <c r="H17" t="inlineStr">
         <is>
           <t>备注</t>
         </is>
       </c>
     </row>
-    <row r="17"/>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>下发</t>
-        </is>
-      </c>
-    </row>
+    <row r="18"/>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>时间</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>金额</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>标记人</t>
-        </is>
-      </c>
-      <c r="D19" t="inlineStr">
-        <is>
-          <t>操作人</t>
-        </is>
-      </c>
-      <c r="E19" t="inlineStr">
-        <is>
-          <t>备注</t>
+          <t>下发</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>09/08 15:27:46</t>
+          <t>时间</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>18181</t>
+          <t>金额</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t/>
+          <t>标记人</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>操作人</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t/>
+          <t>备注</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>09/07 19:03:29</t>
+          <t>09/08 15:27:46</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>11904</t>
+          <t>18181</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -592,12 +607,12 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>09/04 20:59:45</t>
+          <t>09/07 19:03:29</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>11760</t>
+          <t>11904</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -619,12 +634,12 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>09/04 19:57:15</t>
+          <t>09/04 20:59:45</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>288</t>
+          <t>11760</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -634,7 +649,7 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>xinhui9</t>
+          <t>jxxiaomei521</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
@@ -646,12 +661,12 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>09/03 19:40:03</t>
+          <t>09/04 19:57:15</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>5564</t>
+          <t>288</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -661,7 +676,7 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>xinhui9</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
@@ -673,12 +688,12 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>09/03 18:23:33</t>
+          <t>09/03 19:40:03</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>388</t>
+          <t>5564</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -688,7 +703,7 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>jxxiaomei521</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
@@ -700,12 +715,12 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>09/02 11:07:38</t>
+          <t>09/03 18:23:33</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>12195</t>
+          <t>388</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -715,7 +730,7 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
@@ -727,12 +742,12 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>08/25 12:50:23</t>
+          <t>09/02 11:07:38</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>12269</t>
+          <t>12195</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -754,83 +769,110 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
+          <t>08/25 12:50:23</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>12269</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>jxxiaomei521</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
           <t>08/24 09:45:46</t>
         </is>
       </c>
-      <c r="B28" t="inlineStr">
+      <c r="B29" t="inlineStr">
         <is>
           <t>46380</t>
         </is>
       </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="D28" t="inlineStr">
+      <c r="C29" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
         <is>
           <t>jxxiaomei521</t>
         </is>
       </c>
-      <c r="E28" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-    </row>
-    <row r="29"/>
-    <row r="30">
-      <c r="A30" t="inlineStr">
-        <is>
-          <t>总计</t>
-        </is>
-      </c>
-    </row>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="30"/>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>总入款</t>
-        </is>
-      </c>
-      <c r="B31" t="inlineStr">
-        <is>
-          <t>1435800</t>
+          <t>总计</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>应下发</t>
+          <t>总入款</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>174701.19</t>
+          <t>1545800</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>已下发</t>
+          <t>应下发</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>118929</t>
+          <t>187796.42</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
+          <t>已下发</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>118929</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
           <t>未下发</t>
         </is>
       </c>
-      <c r="B34" t="inlineStr">
-        <is>
-          <t>55772.19</t>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>68867.42</t>
         </is>
       </c>
     </row>

--- a/bills/JXZFSP01/-1003733706693/6d85008f7f7972fd90832a1022876df384976a1165aef80c1e3f256d2e720bdf/bill-all.xlsx
+++ b/bills/JXZFSP01/-1003733706693/6d85008f7f7972fd90832a1022876df384976a1165aef80c1e3f256d2e720bdf/bill-all.xlsx
@@ -580,12 +580,12 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>09/08 15:27:46</t>
+          <t>09/09 15:29:43</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>18181</t>
+          <t>9388</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -607,12 +607,12 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>09/07 19:03:29</t>
+          <t>09/08 15:27:46</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>11904</t>
+          <t>18181</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -634,12 +634,12 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>09/04 20:59:45</t>
+          <t>09/07 19:03:29</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>11760</t>
+          <t>11904</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -661,12 +661,12 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>09/04 19:57:15</t>
+          <t>09/04 20:59:45</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>288</t>
+          <t>11760</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -676,7 +676,7 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>xinhui9</t>
+          <t>jxxiaomei521</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
@@ -688,12 +688,12 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>09/03 19:40:03</t>
+          <t>09/04 19:57:15</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>5564</t>
+          <t>288</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -703,7 +703,7 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>xinhui9</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
@@ -715,12 +715,12 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>09/03 18:23:33</t>
+          <t>09/03 19:40:03</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>388</t>
+          <t>5564</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -730,7 +730,7 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>jxxiaomei521</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
@@ -742,12 +742,12 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>09/02 11:07:38</t>
+          <t>09/03 18:23:33</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>12195</t>
+          <t>388</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -757,7 +757,7 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
@@ -769,12 +769,12 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>08/25 12:50:23</t>
+          <t>09/02 11:07:38</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>12269</t>
+          <t>12195</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -796,83 +796,110 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
+          <t>08/25 12:50:23</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>12269</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>jxxiaomei521</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
           <t>08/24 09:45:46</t>
         </is>
       </c>
-      <c r="B29" t="inlineStr">
+      <c r="B30" t="inlineStr">
         <is>
           <t>46380</t>
         </is>
       </c>
-      <c r="C29" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="D29" t="inlineStr">
+      <c r="C30" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
         <is>
           <t>jxxiaomei521</t>
         </is>
       </c>
-      <c r="E29" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-    </row>
-    <row r="30"/>
-    <row r="31">
-      <c r="A31" t="inlineStr">
-        <is>
-          <t>总计</t>
-        </is>
-      </c>
-    </row>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="31"/>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>总入款</t>
-        </is>
-      </c>
-      <c r="B32" t="inlineStr">
-        <is>
-          <t>1545800</t>
+          <t>总计</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>应下发</t>
+          <t>总入款</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>187796.42</t>
+          <t>1545800</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>已下发</t>
+          <t>应下发</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>118929</t>
+          <t>187796.42</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
+          <t>已下发</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>128317</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
           <t>未下发</t>
         </is>
       </c>
-      <c r="B35" t="inlineStr">
-        <is>
-          <t>68867.42</t>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>59479.42</t>
         </is>
       </c>
     </row>

--- a/bills/JXZFSP01/-1003733706693/6d85008f7f7972fd90832a1022876df384976a1165aef80c1e3f256d2e720bdf/bill-all.xlsx
+++ b/bills/JXZFSP01/-1003733706693/6d85008f7f7972fd90832a1022876df384976a1165aef80c1e3f256d2e720bdf/bill-all.xlsx
@@ -75,12 +75,12 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>09/09 14:13:29</t>
+          <t>09/11 10:41:59</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>110000</t>
+          <t>70000</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -95,7 +95,7 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>13095.24</t>
+          <t>8333.33</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -105,7 +105,7 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>xinhui9</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -117,12 +117,12 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>09/09 12:13:06</t>
+          <t>09/09 14:13:29</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>79800</t>
+          <t>110000</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -132,12 +132,12 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>8.5</t>
+          <t>8.4</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>9388.24</t>
+          <t>13095.24</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -159,12 +159,12 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>09/08 13:38:20</t>
+          <t>09/09 12:13:06</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>150000</t>
+          <t>79800</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -174,12 +174,12 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>8.25</t>
+          <t>8.5</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>18181.82</t>
+          <t>9388.24</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -201,12 +201,12 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>09/07 17:02:49</t>
+          <t>09/08 13:38:20</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>100000</t>
+          <t>150000</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -216,12 +216,12 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>8.4</t>
+          <t>8.25</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>11904.76</t>
+          <t>18181.82</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -243,7 +243,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>09/04 19:57:09</t>
+          <t>09/07 17:02:49</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -258,12 +258,12 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>8.3</t>
+          <t>8.4</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>12048.19</t>
+          <t>11904.76</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -285,12 +285,12 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>09/03 18:23:03</t>
+          <t>09/04 19:57:09</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>50000</t>
+          <t>100000</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -300,12 +300,12 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>8.4</t>
+          <t>8.3</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>5952.38</t>
+          <t>12048.19</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -315,7 +315,7 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>xinhui9</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -327,12 +327,12 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>09/02 09:22:19</t>
+          <t>09/03 18:23:03</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>100000</t>
+          <t>50000</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -342,12 +342,12 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>8.2</t>
+          <t>8.4</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>12195.12</t>
+          <t>5952.38</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -357,7 +357,7 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>xinhui9</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -369,7 +369,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>08/25 11:41:35</t>
+          <t>09/02 09:22:19</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -384,12 +384,12 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>8.15</t>
+          <t>8.2</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>12269.94</t>
+          <t>12195.12</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -411,12 +411,12 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>08/24 08:22:11</t>
+          <t>08/25 11:41:35</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>378000</t>
+          <t>100000</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -431,7 +431,7 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>46380.37</t>
+          <t>12269.94</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -441,7 +441,7 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>xinhui9</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
@@ -453,166 +453,181 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
+          <t>08/24 08:22:11</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>378000</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>8.15</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>46380.37</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>tiantiananxin</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
           <t>08/24 08:03:39</t>
         </is>
       </c>
-      <c r="B14" t="inlineStr">
+      <c r="B15" t="inlineStr">
         <is>
           <t>378000</t>
         </is>
       </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="D14" t="inlineStr">
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
         <is>
           <t>8.15</t>
         </is>
       </c>
-      <c r="E14" t="inlineStr">
+      <c r="E15" t="inlineStr">
         <is>
           <t>46380.37</t>
         </is>
       </c>
-      <c r="F14" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="G14" t="inlineStr">
+      <c r="F15" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
         <is>
           <t>xinhui9</t>
         </is>
       </c>
-      <c r="H14" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-    </row>
-    <row r="15"/>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>代付</t>
-        </is>
-      </c>
-    </row>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="16"/>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
+          <t>代付</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
           <t>时间</t>
         </is>
       </c>
-      <c r="B17" t="inlineStr">
+      <c r="B18" t="inlineStr">
         <is>
           <t>金额</t>
         </is>
       </c>
-      <c r="C17" t="inlineStr">
+      <c r="C18" t="inlineStr">
         <is>
           <t>费率</t>
         </is>
       </c>
-      <c r="D17" t="inlineStr">
+      <c r="D18" t="inlineStr">
         <is>
           <t>汇率</t>
         </is>
       </c>
-      <c r="E17" t="inlineStr">
+      <c r="E18" t="inlineStr">
         <is>
           <t>结算</t>
         </is>
       </c>
-      <c r="F17" t="inlineStr">
+      <c r="F18" t="inlineStr">
         <is>
           <t>标记人</t>
         </is>
       </c>
-      <c r="G17" t="inlineStr">
+      <c r="G18" t="inlineStr">
         <is>
           <t>操作人</t>
         </is>
       </c>
-      <c r="H17" t="inlineStr">
+      <c r="H18" t="inlineStr">
         <is>
           <t>备注</t>
         </is>
       </c>
     </row>
-    <row r="18"/>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>下发</t>
-        </is>
-      </c>
-    </row>
+    <row r="19"/>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>时间</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>金额</t>
-        </is>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>标记人</t>
-        </is>
-      </c>
-      <c r="D20" t="inlineStr">
-        <is>
-          <t>操作人</t>
-        </is>
-      </c>
-      <c r="E20" t="inlineStr">
-        <is>
-          <t>备注</t>
+          <t>下发</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>09/09 15:29:43</t>
+          <t>时间</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>9388</t>
+          <t>金额</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t/>
+          <t>标记人</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>操作人</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t/>
+          <t>备注</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>09/08 15:27:46</t>
+          <t>09/09 15:29:43</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>18181</t>
+          <t>9388</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -634,12 +649,12 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>09/07 19:03:29</t>
+          <t>09/08 15:27:46</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>11904</t>
+          <t>18181</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -661,12 +676,12 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>09/04 20:59:45</t>
+          <t>09/07 19:03:29</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>11760</t>
+          <t>11904</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -688,12 +703,12 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>09/04 19:57:15</t>
+          <t>09/04 20:59:45</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>288</t>
+          <t>11760</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -703,7 +718,7 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>xinhui9</t>
+          <t>jxxiaomei521</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
@@ -715,12 +730,12 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>09/03 19:40:03</t>
+          <t>09/04 19:57:15</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>5564</t>
+          <t>288</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -730,7 +745,7 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>xinhui9</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
@@ -742,12 +757,12 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>09/03 18:23:33</t>
+          <t>09/03 19:40:03</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>388</t>
+          <t>5564</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -757,7 +772,7 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>jxxiaomei521</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
@@ -769,12 +784,12 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>09/02 11:07:38</t>
+          <t>09/03 18:23:33</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>12195</t>
+          <t>388</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -784,7 +799,7 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
@@ -796,12 +811,12 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>08/25 12:50:23</t>
+          <t>09/02 11:07:38</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>12269</t>
+          <t>12195</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -823,83 +838,110 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
+          <t>08/25 12:50:23</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>12269</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>jxxiaomei521</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
           <t>08/24 09:45:46</t>
         </is>
       </c>
-      <c r="B30" t="inlineStr">
+      <c r="B31" t="inlineStr">
         <is>
           <t>46380</t>
         </is>
       </c>
-      <c r="C30" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="D30" t="inlineStr">
+      <c r="C31" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
         <is>
           <t>jxxiaomei521</t>
         </is>
       </c>
-      <c r="E30" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-    </row>
-    <row r="31"/>
-    <row r="32">
-      <c r="A32" t="inlineStr">
-        <is>
-          <t>总计</t>
-        </is>
-      </c>
-    </row>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="32"/>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>总入款</t>
-        </is>
-      </c>
-      <c r="B33" t="inlineStr">
-        <is>
-          <t>1545800</t>
+          <t>总计</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>应下发</t>
+          <t>总入款</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>187796.42</t>
+          <t>1615800</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>已下发</t>
+          <t>应下发</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>128317</t>
+          <t>196129.76</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
+          <t>已下发</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>128317</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
           <t>未下发</t>
         </is>
       </c>
-      <c r="B36" t="inlineStr">
-        <is>
-          <t>59479.42</t>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>67812.76</t>
         </is>
       </c>
     </row>

--- a/bills/JXZFSP01/-1003733706693/6d85008f7f7972fd90832a1022876df384976a1165aef80c1e3f256d2e720bdf/bill-all.xlsx
+++ b/bills/JXZFSP01/-1003733706693/6d85008f7f7972fd90832a1022876df384976a1165aef80c1e3f256d2e720bdf/bill-all.xlsx
@@ -622,12 +622,12 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>09/09 15:29:43</t>
+          <t>09/11 12:03:55</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>9388</t>
+          <t>8333</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -649,12 +649,12 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>09/08 15:27:46</t>
+          <t>09/09 15:29:43</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>18181</t>
+          <t>9388</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -676,12 +676,12 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>09/07 19:03:29</t>
+          <t>09/08 15:27:46</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>11904</t>
+          <t>18181</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -703,12 +703,12 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>09/04 20:59:45</t>
+          <t>09/07 19:03:29</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>11760</t>
+          <t>11904</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -730,12 +730,12 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>09/04 19:57:15</t>
+          <t>09/04 20:59:45</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>288</t>
+          <t>11760</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -745,7 +745,7 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>xinhui9</t>
+          <t>jxxiaomei521</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
@@ -757,12 +757,12 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>09/03 19:40:03</t>
+          <t>09/04 19:57:15</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>5564</t>
+          <t>288</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -772,7 +772,7 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>xinhui9</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
@@ -784,12 +784,12 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>09/03 18:23:33</t>
+          <t>09/03 19:40:03</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>388</t>
+          <t>5564</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -799,7 +799,7 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>jxxiaomei521</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
@@ -811,12 +811,12 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>09/02 11:07:38</t>
+          <t>09/03 18:23:33</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>12195</t>
+          <t>388</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -826,7 +826,7 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
@@ -838,12 +838,12 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>08/25 12:50:23</t>
+          <t>09/02 11:07:38</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>12269</t>
+          <t>12195</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -865,83 +865,110 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
+          <t>08/25 12:50:23</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>12269</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>jxxiaomei521</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
           <t>08/24 09:45:46</t>
         </is>
       </c>
-      <c r="B31" t="inlineStr">
+      <c r="B32" t="inlineStr">
         <is>
           <t>46380</t>
         </is>
       </c>
-      <c r="C31" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="D31" t="inlineStr">
+      <c r="C32" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
         <is>
           <t>jxxiaomei521</t>
         </is>
       </c>
-      <c r="E31" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-    </row>
-    <row r="32"/>
-    <row r="33">
-      <c r="A33" t="inlineStr">
-        <is>
-          <t>总计</t>
-        </is>
-      </c>
-    </row>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="33"/>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>总入款</t>
-        </is>
-      </c>
-      <c r="B34" t="inlineStr">
-        <is>
-          <t>1615800</t>
+          <t>总计</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>应下发</t>
+          <t>总入款</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>196129.76</t>
+          <t>1615800</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>已下发</t>
+          <t>应下发</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>128317</t>
+          <t>196129.76</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
+          <t>已下发</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>136650</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
           <t>未下发</t>
         </is>
       </c>
-      <c r="B37" t="inlineStr">
-        <is>
-          <t>67812.76</t>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>59479.76</t>
         </is>
       </c>
     </row>
